--- a/data_lake/industry/CFM/eMMC.xlsx
+++ b/data_lake/industry/CFM/eMMC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E711B7B5-3613-457F-B46E-CF83B3EC91E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14932FC8-A8D2-418D-8595-72BE11A02C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -72,29 +72,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -103,9 +103,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -127,36 +132,36 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -440,19 +445,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -475,7 +480,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -498,7 +503,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -521,7 +526,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -544,7 +549,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -567,7 +572,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -590,7 +595,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -613,7 +618,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -636,7 +641,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -659,7 +664,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -682,7 +687,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -705,7 +710,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -728,7 +733,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -751,7 +756,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -774,7 +779,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -797,7 +802,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -820,7 +825,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -843,7 +848,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -866,7 +871,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -889,7 +894,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -912,7 +917,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -935,7 +940,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -958,7 +963,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -981,7 +986,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1004,7 +1009,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1027,7 +1032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -1050,7 +1055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -1073,7 +1078,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -1096,7 +1101,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -1119,7 +1124,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -1142,7 +1147,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -1165,7 +1170,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -1188,7 +1193,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -1211,7 +1216,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -1234,7 +1239,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -1257,7 +1262,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -1280,7 +1285,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -1303,7 +1308,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -1326,7 +1331,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -1349,7 +1354,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -1372,7 +1377,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -1395,7 +1400,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -1418,7 +1423,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -1441,7 +1446,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -1464,7 +1469,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -1487,7 +1492,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -1510,7 +1515,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -1533,7 +1538,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -1553,6 +1558,121 @@
         <v>20.5</v>
       </c>
       <c r="G48" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F49" s="9">
+        <v>20.5</v>
+      </c>
+      <c r="G49" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F50" s="9">
+        <v>20.5</v>
+      </c>
+      <c r="G50" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F51" s="9">
+        <v>20.5</v>
+      </c>
+      <c r="G51" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F52" s="9">
+        <v>20.5</v>
+      </c>
+      <c r="G52" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F53" s="9">
+        <v>20.5</v>
+      </c>
+      <c r="G53" s="9">
         <v>20</v>
       </c>
     </row>
@@ -1564,19 +1684,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E3458BA-C690-425E-897C-D26F43A0AC55}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1599,7 +1719,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -1622,7 +1742,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -1645,7 +1765,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -1668,7 +1788,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -1691,7 +1811,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -1714,7 +1834,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -1737,7 +1857,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -1760,7 +1880,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -1783,7 +1903,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -1806,7 +1926,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -1829,7 +1949,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -1852,7 +1972,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -1875,7 +1995,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -1898,7 +2018,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -1921,7 +2041,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -1944,7 +2064,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -1967,7 +2087,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -1990,7 +2110,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -2013,7 +2133,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -2036,7 +2156,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -2059,7 +2179,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -2082,7 +2202,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -2105,7 +2225,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -2128,7 +2248,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -2151,7 +2271,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -2174,7 +2294,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -2197,7 +2317,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -2220,7 +2340,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -2243,7 +2363,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -2266,7 +2386,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -2289,7 +2409,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -2312,7 +2432,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -2335,7 +2455,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -2358,7 +2478,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -2381,7 +2501,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -2404,7 +2524,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -2427,7 +2547,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -2450,7 +2570,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -2473,7 +2593,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -2496,7 +2616,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -2519,7 +2639,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -2542,7 +2662,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -2565,7 +2685,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -2588,7 +2708,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -2611,7 +2731,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -2634,7 +2754,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -2657,7 +2777,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -2677,6 +2797,121 @@
         <v>22.3</v>
       </c>
       <c r="G48" s="9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>20.8</v>
+      </c>
+      <c r="F49" s="9">
+        <v>22.3</v>
+      </c>
+      <c r="G49" s="9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>20.8</v>
+      </c>
+      <c r="F50" s="9">
+        <v>22.3</v>
+      </c>
+      <c r="G50" s="9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>20.8</v>
+      </c>
+      <c r="F51" s="9">
+        <v>22.3</v>
+      </c>
+      <c r="G51" s="9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>20.8</v>
+      </c>
+      <c r="F52" s="9">
+        <v>22.3</v>
+      </c>
+      <c r="G52" s="9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>20.8</v>
+      </c>
+      <c r="F53" s="9">
+        <v>22.3</v>
+      </c>
+      <c r="G53" s="9">
         <v>21</v>
       </c>
     </row>
@@ -2688,19 +2923,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A4C3C62-4D14-4156-9017-943BF365E5C9}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2723,7 +2958,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -2746,7 +2981,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -2769,7 +3004,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -2792,7 +3027,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -2815,7 +3050,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -2838,7 +3073,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -2861,7 +3096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -2884,7 +3119,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -2907,7 +3142,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -2930,7 +3165,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -2953,7 +3188,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -2976,7 +3211,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -2999,7 +3234,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -3022,7 +3257,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -3045,7 +3280,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -3068,7 +3303,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -3091,7 +3326,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -3114,7 +3349,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -3137,7 +3372,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -3160,7 +3395,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -3183,7 +3418,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -3206,7 +3441,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -3229,7 +3464,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -3252,7 +3487,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -3275,7 +3510,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -3298,7 +3533,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -3321,7 +3556,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -3344,7 +3579,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -3367,7 +3602,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -3390,7 +3625,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -3413,7 +3648,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -3436,7 +3671,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -3459,7 +3694,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -3482,7 +3717,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -3505,7 +3740,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -3528,7 +3763,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -3551,7 +3786,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -3574,7 +3809,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -3597,7 +3832,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -3620,7 +3855,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -3643,7 +3878,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -3666,7 +3901,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -3689,7 +3924,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -3712,7 +3947,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -3735,7 +3970,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -3758,7 +3993,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -3781,7 +4016,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -3801,6 +4036,121 @@
         <v>24.3</v>
       </c>
       <c r="G48" s="9">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>22.6</v>
+      </c>
+      <c r="F49" s="9">
+        <v>24.3</v>
+      </c>
+      <c r="G49" s="9">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>22.6</v>
+      </c>
+      <c r="F50" s="9">
+        <v>24.3</v>
+      </c>
+      <c r="G50" s="9">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>22.6</v>
+      </c>
+      <c r="F51" s="9">
+        <v>24.3</v>
+      </c>
+      <c r="G51" s="9">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>22.6</v>
+      </c>
+      <c r="F52" s="9">
+        <v>24.3</v>
+      </c>
+      <c r="G52" s="9">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>22.6</v>
+      </c>
+      <c r="F53" s="9">
+        <v>24.3</v>
+      </c>
+      <c r="G53" s="9">
         <v>23</v>
       </c>
     </row>
@@ -3812,19 +4162,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB386A95-5195-4084-9FB9-971921256B62}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3847,7 +4197,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -3870,7 +4220,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -3893,7 +4243,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -3916,7 +4266,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -3939,7 +4289,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -3962,7 +4312,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -3985,7 +4335,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -4008,7 +4358,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -4031,7 +4381,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -4054,7 +4404,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -4077,7 +4427,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -4100,7 +4450,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -4123,7 +4473,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -4146,7 +4496,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -4169,7 +4519,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -4192,7 +4542,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -4215,7 +4565,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -4238,7 +4588,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -4261,7 +4611,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -4284,7 +4634,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -4307,7 +4657,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -4330,7 +4680,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -4353,7 +4703,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -4376,7 +4726,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -4399,7 +4749,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -4422,7 +4772,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -4445,7 +4795,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -4468,7 +4818,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -4491,7 +4841,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -4514,7 +4864,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -4537,7 +4887,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -4560,7 +4910,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -4583,7 +4933,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -4606,7 +4956,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -4629,7 +4979,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -4652,7 +5002,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -4675,7 +5025,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -4698,7 +5048,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -4721,7 +5071,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -4744,7 +5094,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -4767,7 +5117,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -4790,7 +5140,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -4813,7 +5163,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -4836,7 +5186,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -4859,7 +5209,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -4882,7 +5232,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -4905,7 +5255,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -4926,6 +5276,121 @@
       </c>
       <c r="G48" s="9">
         <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>24.5</v>
+      </c>
+      <c r="F49" s="9">
+        <v>26</v>
+      </c>
+      <c r="G49" s="9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>24.5</v>
+      </c>
+      <c r="F50" s="9">
+        <v>26</v>
+      </c>
+      <c r="G50" s="9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>23.5</v>
+      </c>
+      <c r="F51" s="9">
+        <v>25</v>
+      </c>
+      <c r="G51" s="9">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>23.5</v>
+      </c>
+      <c r="F52" s="9">
+        <v>25</v>
+      </c>
+      <c r="G52" s="9">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>23</v>
+      </c>
+      <c r="F53" s="9">
+        <v>24.5</v>
+      </c>
+      <c r="G53" s="9">
+        <v>23.5</v>
       </c>
     </row>
   </sheetData>
@@ -4936,19 +5401,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C29CFE0E-1939-4F13-BC18-8B4E3159446B}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4971,7 +5436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -4994,7 +5459,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -5017,7 +5482,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -5040,7 +5505,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -5063,7 +5528,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -5086,7 +5551,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -5109,7 +5574,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -5132,7 +5597,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -5155,7 +5620,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -5178,7 +5643,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -5201,7 +5666,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -5224,7 +5689,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -5247,7 +5712,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -5270,7 +5735,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -5293,7 +5758,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -5316,7 +5781,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -5339,7 +5804,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -5362,7 +5827,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -5385,7 +5850,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -5408,7 +5873,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -5431,7 +5896,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -5454,7 +5919,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -5477,7 +5942,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -5500,7 +5965,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -5523,7 +5988,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -5546,7 +6011,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -5569,7 +6034,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -5592,7 +6057,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -5615,7 +6080,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -5638,7 +6103,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -5661,7 +6126,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -5684,7 +6149,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -5707,7 +6172,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -5730,7 +6195,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -5753,7 +6218,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -5776,7 +6241,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -5799,7 +6264,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -5822,7 +6287,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -5845,7 +6310,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -5868,7 +6333,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -5891,7 +6356,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -5914,7 +6379,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -5937,7 +6402,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -5960,7 +6425,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -5983,7 +6448,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -6006,7 +6471,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -6029,7 +6494,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -6049,6 +6514,121 @@
         <v>33.5</v>
       </c>
       <c r="G48" s="9">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>30.4</v>
+      </c>
+      <c r="F49" s="9">
+        <v>33.5</v>
+      </c>
+      <c r="G49" s="9">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>30.4</v>
+      </c>
+      <c r="F50" s="9">
+        <v>33.5</v>
+      </c>
+      <c r="G50" s="9">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>30.4</v>
+      </c>
+      <c r="F51" s="9">
+        <v>33.5</v>
+      </c>
+      <c r="G51" s="9">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>30.4</v>
+      </c>
+      <c r="F52" s="9">
+        <v>33.5</v>
+      </c>
+      <c r="G52" s="9">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>30.4</v>
+      </c>
+      <c r="F53" s="9">
+        <v>33.5</v>
+      </c>
+      <c r="G53" s="9">
         <v>31</v>
       </c>
     </row>
@@ -6060,19 +6640,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEFF7D63-8706-4CE6-8EDE-86A6F3873A2B}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6095,7 +6675,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -6118,7 +6698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -6141,7 +6721,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -6164,7 +6744,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -6187,7 +6767,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -6210,7 +6790,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -6233,7 +6813,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -6256,7 +6836,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -6279,7 +6859,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -6302,7 +6882,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -6325,7 +6905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -6348,7 +6928,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -6371,7 +6951,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -6394,7 +6974,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -6417,7 +6997,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -6440,7 +7020,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -6463,7 +7043,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -6486,7 +7066,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -6509,7 +7089,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -6532,7 +7112,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -6555,7 +7135,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -6578,7 +7158,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -6601,7 +7181,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -6624,7 +7204,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -6647,7 +7227,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -6670,7 +7250,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -6693,7 +7273,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -6716,7 +7296,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -6739,7 +7319,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -6762,7 +7342,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -6785,7 +7365,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -6808,7 +7388,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -6831,7 +7411,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -6854,7 +7434,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -6877,7 +7457,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -6900,7 +7480,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -6923,7 +7503,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -6946,7 +7526,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -6969,7 +7549,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -6992,7 +7572,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -7015,7 +7595,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -7038,7 +7618,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -7061,7 +7641,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -7084,7 +7664,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -7107,7 +7687,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -7130,7 +7710,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -7153,7 +7733,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -7173,6 +7753,121 @@
         <v>60.5</v>
       </c>
       <c r="G48" s="9">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>56.1</v>
+      </c>
+      <c r="F49" s="9">
+        <v>60.5</v>
+      </c>
+      <c r="G49" s="9">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>56.1</v>
+      </c>
+      <c r="F50" s="9">
+        <v>60.5</v>
+      </c>
+      <c r="G50" s="9">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>56.1</v>
+      </c>
+      <c r="F51" s="9">
+        <v>60.5</v>
+      </c>
+      <c r="G51" s="9">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>56.1</v>
+      </c>
+      <c r="F52" s="9">
+        <v>60.5</v>
+      </c>
+      <c r="G52" s="9">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>56.1</v>
+      </c>
+      <c r="F53" s="9">
+        <v>60.5</v>
+      </c>
+      <c r="G53" s="9">
         <v>58</v>
       </c>
     </row>
